--- a/src/roles.xlsx
+++ b/src/roles.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="25">
   <si>
     <t>Role</t>
   </si>
@@ -74,6 +74,27 @@
   </si>
   <si>
     <t xml:space="preserve">CommandInvoker </t>
+  </si>
+  <si>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Context</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Abstract State</t>
+  </si>
+  <si>
+    <t>ParserState</t>
+  </si>
+  <si>
+    <t>Concrete States</t>
+  </si>
+  <si>
+    <t>BeforePrologState, InPrologState, OutsideTagState, InsideElementTagState, InsideAttributeState</t>
   </si>
 </sst>
 </file>
@@ -452,8 +473,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac xr xr2 xr3" ns2:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -549,6 +570,43 @@
         <v>15</v>
       </c>
     </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/src/roles.xlsx
+++ b/src/roles.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lfan/Documents/GitHub/2026-spring-software-patterns/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E000E1B-21C4-2644-8760-FB96F241E8A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF267F95-FB3D-BB43-ABBC-9422B4957282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
   <si>
     <t>Role</t>
   </si>
@@ -31,27 +31,6 @@
     <t>Client</t>
   </si>
   <si>
-    <t>State</t>
-  </si>
-  <si>
-    <t>Context</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>Abstract state</t>
-  </si>
-  <si>
-    <t>ParserState</t>
-  </si>
-  <si>
-    <t>Concrete states</t>
-  </si>
-  <si>
-    <t>BeforePrologState, InPrologState, OutsideTagState, InsideElementTagState, InsideAttributeState</t>
-  </si>
-  <si>
     <t>Visitor</t>
   </si>
   <si>
@@ -77,6 +56,39 @@
   </si>
   <si>
     <t>Text, Element, Document, Attr, and their implementations</t>
+  </si>
+  <si>
+    <t>Flyweight</t>
+  </si>
+  <si>
+    <t>FlyweightFactory</t>
+  </si>
+  <si>
+    <t>NodeFlyweightFactory</t>
+  </si>
+  <si>
+    <t>Node_Impl</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NodeFlyweight </t>
+  </si>
+  <si>
+    <t>ConcreteFlyweight</t>
+  </si>
+  <si>
+    <t>ElementFlyweight, AttrFlyweight, TextFlyweight</t>
+  </si>
+  <si>
+    <t>UnsharedConcreteFlyweight</t>
+  </si>
+  <si>
+    <t>DocumentFlyweight</t>
+  </si>
+  <si>
+    <t>Façade</t>
+  </si>
+  <si>
+    <t>Interpreter</t>
   </si>
 </sst>
 </file>
@@ -457,7 +469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -465,7 +477,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -478,87 +490,156 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="A8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="A9" s="2"/>
+      <c r="B9" s="2"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A10" s="1"/>
+      <c r="B10" s="1"/>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A15" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>16</v>
+      <c r="A15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>18</v>
+      <c r="A16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>8</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>10</v>
+      </c>
+      <c r="B18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B28" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/src/roles.xlsx
+++ b/src/roles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lfan/Documents/GitHub/2026-spring-software-patterns/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF267F95-FB3D-BB43-ABBC-9422B4957282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4EEADE-759E-BF4E-9098-F5AD6288CF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
   <si>
     <t>Role</t>
   </si>
@@ -89,6 +89,30 @@
   </si>
   <si>
     <t>Interpreter</t>
+  </si>
+  <si>
+    <t>Test.c</t>
+  </si>
+  <si>
+    <t>Context</t>
+  </si>
+  <si>
+    <t>The parsed DOM</t>
+  </si>
+  <si>
+    <t>AbstractExpression</t>
+  </si>
+  <si>
+    <t>NonterminalExpression</t>
+  </si>
+  <si>
+    <t>Element_Impl</t>
+  </si>
+  <si>
+    <t>TerminalExpression</t>
+  </si>
+  <si>
+    <t>Text_Impl</t>
   </si>
 </sst>
 </file>
@@ -131,10 +155,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,7 +536,7 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7" s="1" t="s">
@@ -521,16 +544,12 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
@@ -554,39 +573,39 @@
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">

--- a/src/roles.xlsx
+++ b/src/roles.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lfan/Documents/GitHub/2026-spring-software-patterns/src/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD4EEADE-759E-BF4E-9098-F5AD6288CF86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA76943-93A3-F240-BA56-3CDD7DB28103}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="24">
   <si>
     <t>Role</t>
   </si>
@@ -31,33 +31,9 @@
     <t>Client</t>
   </si>
   <si>
-    <t>Visitor</t>
-  </si>
-  <si>
-    <t>XMLSerializer</t>
-  </si>
-  <si>
-    <t>Concrete visitor</t>
-  </si>
-  <si>
-    <t>SerializeVisitor</t>
-  </si>
-  <si>
-    <t>PrettySerializeVisitor, MinimalSerializeVisitor</t>
-  </si>
-  <si>
-    <t>Element</t>
-  </si>
-  <si>
     <t>Node</t>
   </si>
   <si>
-    <t>Concrete Element</t>
-  </si>
-  <si>
-    <t>Text, Element, Document, Attr, and their implementations</t>
-  </si>
-  <si>
     <t>Flyweight</t>
   </si>
   <si>
@@ -113,6 +89,9 @@
   </si>
   <si>
     <t>Text_Impl</t>
+  </si>
+  <si>
+    <t>PatternsFacade</t>
   </si>
 </sst>
 </file>
@@ -492,7 +471,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.33203125" customWidth="1"/>
@@ -500,7 +479,7 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
@@ -513,10 +492,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
@@ -524,31 +503,31 @@
         <v>2</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
@@ -557,7 +536,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
@@ -573,44 +552,44 @@
         <v>2</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B17" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.2">
@@ -623,43 +602,19 @@
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A25" s="1"/>
+      <c r="B25" s="1"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>8</v>
-      </c>
-      <c r="B27" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
-        <v>10</v>
-      </c>
-      <c r="B28" t="s">
-        <v>11</v>
-      </c>
+      <c r="A26" s="1"/>
+      <c r="B26" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
